--- a/output/pdf_financials_xlsx/CEQ.xlsx
+++ b/output/pdf_financials_xlsx/CEQ.xlsx
@@ -724,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>119.861</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.996</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.214893</v>
@@ -736,10 +736,10 @@
         <v>0.8100039999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>7.718</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>7.904</v>
       </c>
     </row>
     <row r="10">
@@ -773,10 +773,10 @@
         <v>0.008552000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>7.718</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>7.904</v>
       </c>
     </row>
     <row r="11">
@@ -810,10 +810,10 @@
         <v>-3.795442</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>24.661</v>
+        <v>16.943</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>27.158</v>
+        <v>19.254</v>
       </c>
     </row>
     <row r="12">
@@ -4306,10 +4306,10 @@
         <v>0.004638</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.026381</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.309837</v>
       </c>
       <c r="J103" s="3" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>2.719</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.376806</v>
+        <v>0.350425</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>0.752</v>
@@ -5822,7 +5822,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -7806,7 +7810,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -10362,7 +10370,11 @@
           <t>Prepaids and deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17296,7 +17308,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -21166,7 +21182,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -21191,7 +21211,7 @@
         <v>119.861</v>
       </c>
       <c r="J240" s="5" t="n">
-        <v>-0.996</v>
+        <v>0.996</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -21204,10 +21224,10 @@
         </is>
       </c>
       <c r="M240" s="5" t="n">
-        <v>-7.718</v>
+        <v>7.718</v>
       </c>
       <c r="N240" s="5" t="n">
-        <v>-7.904</v>
+        <v>7.904</v>
       </c>
     </row>
     <row r="241">
@@ -22644,7 +22664,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -22686,7 +22710,7 @@
         </is>
       </c>
       <c r="M264" s="5" t="n">
-        <v>-7.718</v>
+        <v>7.718</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CEQ.xlsx
+++ b/output/pdf_financials_xlsx/CEQ.xlsx
@@ -761,10 +761,10 @@
         <v>0.126005</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.096857</v>
+        <v>133.308</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.242338</v>
+        <v>13.95</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.011165</v>
@@ -773,10 +773,10 @@
         <v>0.008552000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.718</v>
+        <v>34.57</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>7.904</v>
+        <v>40.947</v>
       </c>
     </row>
     <row r="11">
@@ -798,10 +798,10 @@
         <v>-0.099526</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>100.444143</v>
+        <v>-32.767</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.832662</v>
+        <v>-9.875</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-1.330084</v>
@@ -810,10 +810,10 @@
         <v>-3.795442</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.943</v>
+        <v>-9.909000000000001</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>19.254</v>
+        <v>-13.789</v>
       </c>
     </row>
     <row r="12">
@@ -826,25 +826,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000836</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000833</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000783</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00096</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003236</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1451,19 +1451,19 @@
         <v>-0.06339500000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.099526</v>
+        <v>-0.100359</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-32.767</v>
+        <v>-32.767783</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.875</v>
+        <v>-9.875959999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.323145</v>
+        <v>-1.323595</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.618</v>
+        <v>-7.621236</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-9.909000000000001</v>
@@ -1529,19 +1529,19 @@
         <v>-0.06339500000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.099526</v>
+        <v>-0.100359</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>27.631</v>
+        <v>27.630217</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.115</v>
+        <v>-9.115959999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.314219</v>
+        <v>-1.314669</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.582</v>
+        <v>-7.585236</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-5.46</v>
@@ -1570,13 +1570,13 @@
         <v>-176.7650011153246</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-375.8676687186072</v>
+        <v>-379.0135579138185</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>27.48232064530888</v>
+        <v>27.48154185854527</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-223.680981595092</v>
+        <v>-223.7045398773006</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-6955.963302752293</v>
+        <v>-6958.932110091743</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-22.14022140221402</v>
@@ -1709,7 +1709,7 @@
         <v>0.065946</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.720751</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.433</v>
@@ -1783,7 +1783,7 @@
         <v>0.065946</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.720751</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.433</v>
@@ -2227,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.747132</v>
+        <v>0.026381</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>9.262</v>
@@ -6266,7 +6266,11 @@
           <t>Decommissioning and reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -8422,7 +8426,11 @@
           <t>Decommissioning and reclamation deposits</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -10170,7 +10178,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -10708,7 +10716,11 @@
           <t>Reclamation deposit (Note 13)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -11938,7 +11950,11 @@
           <t>Reclamation deposit (note 7)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -12620,7 +12636,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -14978,7 +14998,11 @@
           <t>Accrued Interest on reclamation deposits</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -18892,7 +18916,11 @@
           <t>Accrued interest on reclamation deposits</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -22220,7 +22248,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -25870,7 +25898,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -26324,7 +26352,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEQ.xlsx
+++ b/output/pdf_financials_xlsx/CEQ.xlsx
@@ -2870,13 +2870,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>5.758</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>3.238</v>
       </c>
     </row>
     <row r="65">
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>3.684</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="68">
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.136697</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.10841</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -3126,10 +3126,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.136697</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.10841</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -3274,10 +3274,10 @@
         <v>0.13632</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.680661</v>
+        <v>1.543964</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>7.853</v>
+        <v>7.74459</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>28.718</v>
@@ -3470,15 +3470,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.03406960520760484</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.1073366336633663</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>29.06578947368421</v>
@@ -4550,16 +4546,16 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.0007649999999999999</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003749</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.00113</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.000646</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -11120,7 +11116,11 @@
           <t>Current portion of lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -11382,7 +11382,11 @@
           <t>Lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -13280,7 +13284,11 @@
           <t>Deferred income tax expense (recovery) 18</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -15068,7 +15076,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -19698,7 +19710,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -23872,7 +23888,11 @@
           <t>Income taxes (recovery) (Note 18)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
